--- a/data/munkadij.xlsx
+++ b/data/munkadij.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/munka/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,30 +41,33 @@
     <t>nev</t>
   </si>
   <si>
+    <t>leiras</t>
+  </si>
+  <si>
     <t>szamtip</t>
   </si>
   <si>
     <t>ar</t>
   </si>
   <si>
-    <t>leiras</t>
-  </si>
-  <si>
     <t>Szabás, gyalulás</t>
   </si>
   <si>
+    <t>Teljes_Felulet</t>
+  </si>
+  <si>
     <t>Anyagbeszerzes</t>
   </si>
   <si>
+    <t>Ora</t>
+  </si>
+  <si>
     <t>Táblásítás</t>
   </si>
   <si>
     <t>Terulet</t>
   </si>
   <si>
-    <t>Ora</t>
-  </si>
-  <si>
     <t>Csiszolás, felületkezelés</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
     <t>Beszerelés</t>
   </si>
   <si>
-    <t>Teljes_Felulet</t>
-  </si>
-  <si>
     <t>Korpusz összeállítás</t>
   </si>
   <si>
@@ -104,26 +104,26 @@
     <t>Kontraprofilos keres, platolt betét</t>
   </si>
   <si>
+    <t>Rövidcsapos, lemez betét</t>
+  </si>
+  <si>
+    <t>Butorlap</t>
+  </si>
+  <si>
+    <t>Tolóajtó</t>
+  </si>
+  <si>
     <t>Fiók készítés</t>
   </si>
   <si>
     <t>FDS classic</t>
-  </si>
-  <si>
-    <t>Rövidcsapos, lemez betét</t>
-  </si>
-  <si>
-    <t>Butorlap</t>
-  </si>
-  <si>
-    <t>Tolóajtó</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,7 +157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normál" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -170,10 +170,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,124 +490,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F996A3D-9C33-4778-8573-93E27149BB42}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>8000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>5000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>12000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>8000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>15000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>3000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>5000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -619,13 +615,13 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -633,13 +629,13 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>40000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -647,63 +643,63 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>15000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>30000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>10000</v>
